--- a/artfynd/A 22117-2026 artfynd.xlsx
+++ b/artfynd/A 22117-2026 artfynd.xlsx
@@ -1042,7 +1042,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134225067</v>
+        <v>134217662</v>
       </c>
       <c r="B5" t="n">
         <v>79358</v>
@@ -1071,19 +1071,22 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lång-Mjösjön, Ång</t>
+          <t>Lång Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>652937</v>
+        <v>652662</v>
       </c>
       <c r="R5" t="n">
-        <v>7003800</v>
+        <v>7003977</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,39 +1113,65 @@
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134217662</v>
+        <v>134217655</v>
       </c>
       <c r="B6" t="n">
-        <v>79358</v>
+        <v>80473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,21 +1179,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,13 +1206,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>652662</v>
+        <v>652944</v>
       </c>
       <c r="R6" t="n">
-        <v>7003977</v>
+        <v>7003831</v>
       </c>
       <c r="S6" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,7 +1241,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1251,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,17 +1266,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1258,17 +1287,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Susanne Rantakokko</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134217655</v>
+        <v>134225067</v>
       </c>
       <c r="B7" t="n">
-        <v>80473</v>
+        <v>79358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,37 +1305,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lång Mjösjön, Ång</t>
+          <t>Lång-Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>652944</v>
+        <v>652937</v>
       </c>
       <c r="R7" t="n">
-        <v>7003831</v>
+        <v>7003800</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1336,55 +1362,29 @@
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Susanne Rantakokko</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 22117-2026 artfynd.xlsx
+++ b/artfynd/A 22117-2026 artfynd.xlsx
@@ -1838,7 +1838,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134225073</v>
+        <v>134217648</v>
       </c>
       <c r="B12" t="n">
         <v>79358</v>
@@ -1867,19 +1867,22 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lång-Mjösjön, Ång</t>
+          <t>Lång Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>652689</v>
+        <v>652934</v>
       </c>
       <c r="R12" t="n">
-        <v>7003973</v>
+        <v>7003922</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1906,36 +1909,62 @@
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134225074</v>
+        <v>134225073</v>
       </c>
       <c r="B13" t="n">
         <v>79358</v>
@@ -1970,13 +1999,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>652579</v>
+        <v>652689</v>
       </c>
       <c r="R13" t="n">
-        <v>7004056</v>
+        <v>7003973</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2032,7 +2061,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134217648</v>
+        <v>134225074</v>
       </c>
       <c r="B14" t="n">
         <v>79358</v>
@@ -2061,22 +2090,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lång Mjösjön, Ång</t>
+          <t>Lång-Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>652934</v>
+        <v>652579</v>
       </c>
       <c r="R14" t="n">
-        <v>7003922</v>
+        <v>7004056</v>
       </c>
       <c r="S14" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2103,55 +2129,29 @@
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 22117-2026 artfynd.xlsx
+++ b/artfynd/A 22117-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>134217656</v>
       </c>
       <c r="B3" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>134217654</v>
       </c>
       <c r="B4" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134217662</v>
+        <v>134225067</v>
       </c>
       <c r="B5" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,22 +1071,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lång Mjösjön, Ång</t>
+          <t>Lång-Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>652662</v>
+        <v>652937</v>
       </c>
       <c r="R5" t="n">
-        <v>7003977</v>
+        <v>7003800</v>
       </c>
       <c r="S5" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,65 +1110,39 @@
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134217655</v>
+        <v>134217662</v>
       </c>
       <c r="B6" t="n">
-        <v>80473</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1206,13 +1177,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>652944</v>
+        <v>652662</v>
       </c>
       <c r="R6" t="n">
-        <v>7003831</v>
+        <v>7003977</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1251,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,17 +1237,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1287,17 +1258,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Susanne Rantakokko</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134225067</v>
+        <v>134217655</v>
       </c>
       <c r="B7" t="n">
-        <v>79358</v>
+        <v>80474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,34 +1276,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lång-Mjösjön, Ång</t>
+          <t>Lång Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>652937</v>
+        <v>652944</v>
       </c>
       <c r="R7" t="n">
-        <v>7003800</v>
+        <v>7003831</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1362,29 +1336,55 @@
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja, Ann-Christine Borja, Susanne Rantakokko</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1394,7 +1394,7 @@
         <v>134217661</v>
       </c>
       <c r="B8" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>134225072</v>
       </c>
       <c r="B9" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>134225065</v>
       </c>
       <c r="B10" t="n">
-        <v>92349</v>
+        <v>92351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>134217660</v>
       </c>
       <c r="B11" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>134217648</v>
       </c>
       <c r="B12" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>134225073</v>
       </c>
       <c r="B13" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>134225074</v>
       </c>
       <c r="B14" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2158,48 +2158,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134217666</v>
+        <v>134225075</v>
       </c>
       <c r="B15" t="n">
-        <v>98043</v>
+        <v>79359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lång Mjösjön, Ång</t>
+          <t>Lång-Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>652841</v>
+        <v>652711</v>
       </c>
       <c r="R15" t="n">
-        <v>7004023</v>
+        <v>7004094</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2226,19 +2226,9 @@
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,63 +2243,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134217646</v>
+        <v>134217666</v>
       </c>
       <c r="B16" t="n">
-        <v>79358</v>
+        <v>98045</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lång Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>652937</v>
+        <v>652841</v>
       </c>
       <c r="R16" t="n">
-        <v>7003942</v>
+        <v>7004023</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2338,7 +2325,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2335,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2357,24 +2344,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2391,10 +2362,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134217649</v>
+        <v>134217646</v>
       </c>
       <c r="B17" t="n">
-        <v>91957</v>
+        <v>79359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,21 +2373,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2429,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>652960</v>
+        <v>652937</v>
       </c>
       <c r="R17" t="n">
-        <v>7003901</v>
+        <v>7003942</v>
       </c>
       <c r="S17" t="n">
         <v>12</v>
@@ -2464,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2474,7 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,6 +2458,21 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
@@ -2495,17 +2481,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Maria Danvind, Vivien Renaut, Susanne Rantakokko</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134225075</v>
+        <v>134217649</v>
       </c>
       <c r="B18" t="n">
-        <v>79358</v>
+        <v>91959</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2513,34 +2499,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lång-Mjösjön, Ång</t>
+          <t>Lång Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>652711</v>
+        <v>652960</v>
       </c>
       <c r="R18" t="n">
-        <v>7004094</v>
+        <v>7003901</v>
       </c>
       <c r="S18" t="n">
         <v>12</v>
@@ -2570,39 +2559,50 @@
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja, Ann-Christine Borja, Maria Danvind, Vivien Renaut, Susanne Rantakokko</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134217663</v>
+        <v>134225068</v>
       </c>
       <c r="B19" t="n">
-        <v>91957</v>
+        <v>79359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,40 +2610,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lång Mjösjön, Ång</t>
+          <t>Lång-Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>652656</v>
+        <v>652879</v>
       </c>
       <c r="R19" t="n">
-        <v>7004024</v>
+        <v>7003823</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2670,50 +2667,39 @@
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Maria Danvind, Vivien Renaut, Susanne Rantakokko</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134225068</v>
+        <v>134217663</v>
       </c>
       <c r="B20" t="n">
-        <v>79358</v>
+        <v>91959</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2721,37 +2707,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lång-Mjösjön, Ång</t>
+          <t>Lång Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>652879</v>
+        <v>652656</v>
       </c>
       <c r="R20" t="n">
-        <v>7003823</v>
+        <v>7004024</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2778,29 +2767,40 @@
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja, Ann-Christine Borja, Maria Danvind, Vivien Renaut, Susanne Rantakokko</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2810,7 +2810,7 @@
         <v>134217657</v>
       </c>
       <c r="B21" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>134217658</v>
       </c>
       <c r="B22" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>134225064</v>
       </c>
       <c r="B23" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>134225071</v>
       </c>
       <c r="B24" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>134217664</v>
       </c>
       <c r="B25" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>134217647</v>
       </c>
       <c r="B26" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>134217651</v>
       </c>
       <c r="B27" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>134225066</v>
       </c>
       <c r="B28" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>134225070</v>
       </c>
       <c r="B29" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>134225069</v>
       </c>
       <c r="B30" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 22117-2026 artfynd.xlsx
+++ b/artfynd/A 22117-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217649</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217663</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225063</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225064</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217646</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217647</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1466,6 +1501,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217648</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1592,6 +1632,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217650</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1718,6 +1763,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217651</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1844,6 +1894,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217654</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1970,6 +2025,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217656</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2096,6 +2156,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217657</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2222,6 +2287,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217658</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2348,6 +2418,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217660</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2474,6 +2549,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217661</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2600,6 +2680,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217662</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2726,6 +2811,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217664</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2823,6 +2913,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225066</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2920,6 +3015,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225067</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3017,6 +3117,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225068</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3114,6 +3219,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225069</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3211,6 +3321,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225070</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3308,6 +3423,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225071</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3405,6 +3525,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225072</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3502,6 +3627,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225073</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3599,6 +3729,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225074</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3696,6 +3831,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225075</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3793,6 +3933,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225077</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3919,6 +4064,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217655</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4034,6 +4184,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217653</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4141,6 +4296,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217666</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4239,8 +4399,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225065</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>